--- a/Matryca_ADR.xlsx
+++ b/Matryca_ADR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\git\TicketStream\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A226B9F8-EAEC-48F1-A6C9-D6E3960CA01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3234298-1622-4C89-99E2-1387A7E5C0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matryca decyzji" sheetId="1" r:id="rId1"/>
@@ -1752,9 +1752,6 @@
     <t>Node.js + Express; Java + Spring Boot; Python + FastAPI</t>
   </si>
   <si>
-    <t>Zespół TicketStream</t>
-  </si>
-  <si>
     <t>Użytkownik musi widzieć zmiany miejsc niemal natychmiast, a zadania poboczne nie mogą blokować API.</t>
   </si>
   <si>
@@ -2059,6 +2056,9 @@
   </si>
   <si>
     <t>Osobny skrypt inicjalizacyjny; tworzenie danych przez punkty końcowe administracyjne; brak danych inicjalnych</t>
+  </si>
+  <si>
+    <t>Oliwia Gierlicka, Jakub Kierasiński, Jakub Olcha</t>
   </si>
 </sst>
 </file>
@@ -4563,7 +4563,7 @@
         <v>394</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>494</v>
+        <v>596</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
@@ -4595,19 +4595,19 @@
         <v>254</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>524</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>525</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>493</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>526</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4618,16 +4618,16 @@
         <v>491</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>492</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>522</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4638,16 +4638,16 @@
         <v>490</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>519</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4658,16 +4658,16 @@
         <v>488</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>489</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>516</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4675,19 +4675,19 @@
         <v>278</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4698,16 +4698,16 @@
         <v>487</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4715,19 +4715,19 @@
         <v>290</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>506</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4735,19 +4735,19 @@
         <v>395</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>502</v>
-      </c>
       <c r="E13" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>589</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4758,16 +4758,16 @@
         <v>486</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>498</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -4775,219 +4775,219 @@
         <v>397</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>563</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="48" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>530</v>
-      </c>
       <c r="D16" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>560</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>587</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>583</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="48" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>536</v>
-      </c>
       <c r="C19" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>579</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="48" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>539</v>
-      </c>
       <c r="D20" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>577</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>542</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>574</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="48" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>544</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="48" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="D23" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>596</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="D24" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>569</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>552</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>553</v>
       </c>
     </row>
   </sheetData>
